--- a/research/traditional_assets/database/data/taiwan/taiwan_reinsurance.xlsx
+++ b/research/traditional_assets/database/data/taiwan/taiwan_reinsurance.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0806</v>
+        <v>0.0588</v>
       </c>
       <c r="E2">
-        <v>0.155</v>
+        <v>-0.19</v>
       </c>
       <c r="G2">
-        <v>0.1112171187133706</v>
+        <v>0.1672382818879634</v>
       </c>
       <c r="H2">
-        <v>0.1112171187133706</v>
+        <v>0.1672382818879634</v>
       </c>
       <c r="I2">
-        <v>0.1251192585525419</v>
+        <v>-0.08018944961620121</v>
       </c>
       <c r="J2">
-        <v>0.1052483668847089</v>
+        <v>-0.08018944961620121</v>
       </c>
       <c r="K2">
-        <v>62.4</v>
+        <v>15.4</v>
       </c>
       <c r="L2">
-        <v>0.08504838489845985</v>
+        <v>0.025151069737057</v>
       </c>
       <c r="M2">
-        <v>27.6</v>
+        <v>33.4</v>
       </c>
       <c r="N2">
-        <v>0.04373316431627317</v>
+        <v>0.07348734873487349</v>
       </c>
       <c r="O2">
-        <v>0.4423076923076923</v>
+        <v>2.168831168831169</v>
       </c>
       <c r="P2">
-        <v>27.6</v>
+        <v>33.4</v>
       </c>
       <c r="Q2">
-        <v>0.04373316431627317</v>
+        <v>0.07348734873487349</v>
       </c>
       <c r="R2">
-        <v>0.4423076923076923</v>
+        <v>2.168831168831169</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,55 +636,46 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>661.4</v>
+        <v>664.9</v>
       </c>
       <c r="V2">
-        <v>1.048011408651561</v>
+        <v>1.462926292629263</v>
       </c>
       <c r="W2">
-        <v>0.1433823529411765</v>
+        <v>0.02737777777777778</v>
       </c>
       <c r="X2">
-        <v>0.08136476553948871</v>
+        <v>0.114810171078925</v>
       </c>
       <c r="Y2">
-        <v>0.06201758740168775</v>
-      </c>
-      <c r="Z2">
-        <v>-4.676673996876692</v>
-      </c>
-      <c r="AA2">
-        <v>-0.4922123006234558</v>
+        <v>-0.08743239330114724</v>
       </c>
       <c r="AB2">
-        <v>0.08135993972849577</v>
-      </c>
-      <c r="AC2">
-        <v>-0.5735722403519516</v>
+        <v>0.1148032883027984</v>
       </c>
       <c r="AD2">
-        <v>0.052</v>
+        <v>0.044</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.052</v>
+        <v>0.044</v>
       </c>
       <c r="AG2">
-        <v>-661.348</v>
+        <v>-664.856</v>
       </c>
       <c r="AH2">
-        <v>8.238902831647526e-05</v>
+        <v>9.680030976099124e-05</v>
       </c>
       <c r="AI2">
-        <v>9.243589925909071e-05</v>
+        <v>0.00010172375527114</v>
       </c>
       <c r="AJ2">
-        <v>21.86418936789214</v>
+        <v>3.160622943961665</v>
       </c>
       <c r="AK2">
-        <v>6.690555195856267</v>
+        <v>2.861367900979531</v>
       </c>
       <c r="AL2">
         <v>0.001</v>
@@ -693,16 +684,16 @@
         <v>0.001</v>
       </c>
       <c r="AN2">
-        <v>0.0005639913232104121</v>
+        <v>-0.0009072164948453607</v>
       </c>
       <c r="AO2">
-        <v>91800</v>
+        <v>-49100</v>
       </c>
       <c r="AP2">
-        <v>-7.172971800433839</v>
+        <v>13.70837113402062</v>
       </c>
       <c r="AQ2">
-        <v>91800</v>
+        <v>-49100</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +713,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0806</v>
+        <v>0.0588</v>
       </c>
       <c r="E3">
-        <v>0.155</v>
+        <v>-0.19</v>
       </c>
       <c r="G3">
-        <v>0.1112171187133706</v>
+        <v>0.1672382818879634</v>
       </c>
       <c r="H3">
-        <v>0.1112171187133706</v>
+        <v>0.1672382818879634</v>
       </c>
       <c r="I3">
-        <v>0.1251192585525419</v>
+        <v>-0.08018944961620121</v>
       </c>
       <c r="J3">
-        <v>0.1052483668847089</v>
+        <v>-0.08018944961620121</v>
       </c>
       <c r="K3">
-        <v>62.4</v>
+        <v>15.4</v>
       </c>
       <c r="L3">
-        <v>0.08504838489845985</v>
+        <v>0.025151069737057</v>
       </c>
       <c r="M3">
-        <v>27.6</v>
+        <v>33.4</v>
       </c>
       <c r="N3">
-        <v>0.04373316431627317</v>
+        <v>0.07348734873487349</v>
       </c>
       <c r="O3">
-        <v>0.4423076923076923</v>
+        <v>2.168831168831169</v>
       </c>
       <c r="P3">
-        <v>27.6</v>
+        <v>33.4</v>
       </c>
       <c r="Q3">
-        <v>0.04373316431627317</v>
+        <v>0.07348734873487349</v>
       </c>
       <c r="R3">
-        <v>0.4423076923076923</v>
+        <v>2.168831168831169</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,55 +761,46 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>661.4</v>
+        <v>664.9</v>
       </c>
       <c r="V3">
-        <v>1.048011408651561</v>
+        <v>1.462926292629263</v>
       </c>
       <c r="W3">
-        <v>0.1433823529411765</v>
+        <v>0.02737777777777778</v>
       </c>
       <c r="X3">
-        <v>0.08136476553948871</v>
+        <v>0.114810171078925</v>
       </c>
       <c r="Y3">
-        <v>0.06201758740168775</v>
-      </c>
-      <c r="Z3">
-        <v>-4.676673996876692</v>
-      </c>
-      <c r="AA3">
-        <v>-0.4922123006234558</v>
+        <v>-0.08743239330114724</v>
       </c>
       <c r="AB3">
-        <v>0.08135993972849577</v>
-      </c>
-      <c r="AC3">
-        <v>-0.5735722403519516</v>
+        <v>0.1148032883027984</v>
       </c>
       <c r="AD3">
-        <v>0.052</v>
+        <v>0.044</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.052</v>
+        <v>0.044</v>
       </c>
       <c r="AG3">
-        <v>-661.348</v>
+        <v>-664.856</v>
       </c>
       <c r="AH3">
-        <v>8.238902831647526e-05</v>
+        <v>9.680030976099124e-05</v>
       </c>
       <c r="AI3">
-        <v>9.243589925909071e-05</v>
+        <v>0.00010172375527114</v>
       </c>
       <c r="AJ3">
-        <v>21.86418936789214</v>
+        <v>3.160622943961665</v>
       </c>
       <c r="AK3">
-        <v>6.690555195856267</v>
+        <v>2.861367900979531</v>
       </c>
       <c r="AL3">
         <v>0.001</v>
@@ -827,16 +809,16 @@
         <v>0.001</v>
       </c>
       <c r="AN3">
-        <v>0.0005639913232104121</v>
+        <v>-0.0009072164948453607</v>
       </c>
       <c r="AO3">
-        <v>91800</v>
+        <v>-49100</v>
       </c>
       <c r="AP3">
-        <v>-7.172971800433839</v>
+        <v>13.70837113402062</v>
       </c>
       <c r="AQ3">
-        <v>91800</v>
+        <v>-49100</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/taiwan/taiwan_reinsurance.xlsx
+++ b/research/traditional_assets/database/data/taiwan/taiwan_reinsurance.xlsx
@@ -588,70 +588,67 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0588</v>
+        <v>0.0775</v>
       </c>
       <c r="E2">
-        <v>-0.19</v>
+        <v>0.116</v>
       </c>
       <c r="G2">
-        <v>0.1672382818879634</v>
+        <v>-0.07565337001375516</v>
       </c>
       <c r="H2">
-        <v>0.1672382818879634</v>
+        <v>-0.07565337001375516</v>
       </c>
       <c r="I2">
-        <v>-0.08018944961620121</v>
+        <v>0.07748739110499772</v>
       </c>
       <c r="J2">
-        <v>-0.08018944961620121</v>
+        <v>0.06588282009262247</v>
       </c>
       <c r="K2">
-        <v>15.4</v>
+        <v>53.3</v>
       </c>
       <c r="L2">
-        <v>0.025151069737057</v>
+        <v>0.08146110346935656</v>
       </c>
       <c r="M2">
-        <v>33.4</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.07348734873487349</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>2.168831168831169</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>33.4</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.07348734873487349</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>2.168831168831169</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
       <c r="U2">
-        <v>664.9</v>
+        <v>513.9</v>
       </c>
       <c r="V2">
-        <v>1.462926292629263</v>
+        <v>0.8533709730986382</v>
       </c>
       <c r="W2">
-        <v>0.02737777777777778</v>
+        <v>0.1232369942196532</v>
       </c>
       <c r="X2">
-        <v>0.114810171078925</v>
+        <v>0.09743185930439524</v>
       </c>
       <c r="Y2">
-        <v>-0.08743239330114724</v>
+        <v>0.02580513491525793</v>
       </c>
       <c r="AB2">
-        <v>0.1148032883027984</v>
+        <v>0.09742775528274916</v>
       </c>
       <c r="AD2">
         <v>0.044</v>
@@ -663,19 +660,19 @@
         <v>0.044</v>
       </c>
       <c r="AG2">
-        <v>-664.856</v>
+        <v>-513.856</v>
       </c>
       <c r="AH2">
-        <v>9.680030976099124e-05</v>
+        <v>7.306008860196198e-05</v>
       </c>
       <c r="AI2">
-        <v>0.00010172375527114</v>
+        <v>7.754069124001663e-05</v>
       </c>
       <c r="AJ2">
-        <v>3.160622943961665</v>
+        <v>-5.816535361767632</v>
       </c>
       <c r="AK2">
-        <v>2.861367900979531</v>
+        <v>-9.596892275511731</v>
       </c>
       <c r="AL2">
         <v>0.001</v>
@@ -684,16 +681,16 @@
         <v>0.001</v>
       </c>
       <c r="AN2">
-        <v>-0.0009072164948453607</v>
+        <v>0.0008527131782945736</v>
       </c>
       <c r="AO2">
-        <v>-49100</v>
+        <v>50700</v>
       </c>
       <c r="AP2">
-        <v>13.70837113402062</v>
+        <v>-9.958449612403101</v>
       </c>
       <c r="AQ2">
-        <v>-49100</v>
+        <v>50700</v>
       </c>
     </row>
     <row r="3">
@@ -713,70 +710,67 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0588</v>
+        <v>0.0775</v>
       </c>
       <c r="E3">
-        <v>-0.19</v>
+        <v>0.116</v>
       </c>
       <c r="G3">
-        <v>0.1672382818879634</v>
+        <v>-0.07565337001375516</v>
       </c>
       <c r="H3">
-        <v>0.1672382818879634</v>
+        <v>-0.07565337001375516</v>
       </c>
       <c r="I3">
-        <v>-0.08018944961620121</v>
+        <v>0.07748739110499772</v>
       </c>
       <c r="J3">
-        <v>-0.08018944961620121</v>
+        <v>0.06588282009262247</v>
       </c>
       <c r="K3">
-        <v>15.4</v>
+        <v>53.3</v>
       </c>
       <c r="L3">
-        <v>0.025151069737057</v>
+        <v>0.08146110346935656</v>
       </c>
       <c r="M3">
-        <v>33.4</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.07348734873487349</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>2.168831168831169</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>33.4</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.07348734873487349</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>2.168831168831169</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>664.9</v>
+        <v>513.9</v>
       </c>
       <c r="V3">
-        <v>1.462926292629263</v>
+        <v>0.8533709730986382</v>
       </c>
       <c r="W3">
-        <v>0.02737777777777778</v>
+        <v>0.1232369942196532</v>
       </c>
       <c r="X3">
-        <v>0.114810171078925</v>
+        <v>0.09743185930439524</v>
       </c>
       <c r="Y3">
-        <v>-0.08743239330114724</v>
+        <v>0.02580513491525793</v>
       </c>
       <c r="AB3">
-        <v>0.1148032883027984</v>
+        <v>0.09742775528274916</v>
       </c>
       <c r="AD3">
         <v>0.044</v>
@@ -788,19 +782,19 @@
         <v>0.044</v>
       </c>
       <c r="AG3">
-        <v>-664.856</v>
+        <v>-513.856</v>
       </c>
       <c r="AH3">
-        <v>9.680030976099124e-05</v>
+        <v>7.306008860196198e-05</v>
       </c>
       <c r="AI3">
-        <v>0.00010172375527114</v>
+        <v>7.754069124001663e-05</v>
       </c>
       <c r="AJ3">
-        <v>3.160622943961665</v>
+        <v>-5.816535361767632</v>
       </c>
       <c r="AK3">
-        <v>2.861367900979531</v>
+        <v>-9.596892275511731</v>
       </c>
       <c r="AL3">
         <v>0.001</v>
@@ -809,16 +803,16 @@
         <v>0.001</v>
       </c>
       <c r="AN3">
-        <v>-0.0009072164948453607</v>
+        <v>0.0008527131782945736</v>
       </c>
       <c r="AO3">
-        <v>-49100</v>
+        <v>50700</v>
       </c>
       <c r="AP3">
-        <v>13.70837113402062</v>
+        <v>-9.958449612403101</v>
       </c>
       <c r="AQ3">
-        <v>-49100</v>
+        <v>50700</v>
       </c>
     </row>
   </sheetData>
